--- a/public/rl2.xlsx
+++ b/public/rl2.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Лист 1" sheetId="19" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" calcMode="autoNoTable" iterateCount="1000" iterateDelta="9.9999999999999995E-8"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="28">
   <si>
     <t>АО "СТОКМАНН"</t>
   </si>
@@ -878,7 +878,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1140,44 +1140,27 @@
       <c r="B18" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="30"/>
+      <c r="C18" s="31"/>
       <c r="D18" s="31"/>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="33"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
       <c r="I18" s="2"/>
     </row>
-    <row r="19" spans="1:9" s="3" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="19"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="6">
